--- a/docs/qa/upload-templates/project_plan_upload_template.xlsx
+++ b/docs/qa/upload-templates/project_plan_upload_template.xlsx
@@ -128,57 +128,37 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>IPE QA</author>
+    <author>IPE</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>required; same on all rows</t>
+        <t>Must match seeded erp_mo_id (e.g. MO-ST-001)</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>required</t>
+        <t>UI upload: Planning → Schedule (.xlsx only, max 5MB)</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>required; must exist as erp_mo_id</t>
+        <t>Must match WC code</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>int; unique per MO</t>
+        <t>UI upload: Planning → Schedule (.xlsx only, max 5MB)</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>text</t>
+        <t>UI upload: Planning → Schedule (.xlsx only, max 5MB)</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>WC001|WC002|WC003…</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>number &gt;=0 hours from horizon</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>number &gt;0</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>planned|frozen|disrupted|ai_suggested</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>optional</t>
+        <t>UI upload: Planning → Schedule (.xlsx only, max 5MB)</t>
       </text>
     </comment>
   </commentList>
@@ -474,193 +454,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>PLAN_CODE</t>
+          <t>MO_ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>PLAN_NAME</t>
+          <t>OPERATION_SEQ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>MO_ID</t>
+          <t>WORK_CENTER_CODE</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>OPERATION_SEQUENCE</t>
+          <t>PLANNED_START</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>OPERATION_NAME</t>
+          <t>PLANNED_END</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>WORK_CENTER_CODE</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>START_HOUR</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>DURATION_HOURS</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>NOTES</t>
+          <t>DURATION_HRS</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLAN-STARTRANS-W12</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Star Trans Week 12 Production</t>
-        </is>
+          <t>MO-ST-001</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MO-ST-001</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
+          <t>WC-WND</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wind LV/HV Coils</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>WC002</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Copper expedite lane</t>
-        </is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLAN-STARTRANS-W12</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Star Trans Week 12 Production</t>
-        </is>
+          <t>MO-ST-001</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>20</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MO-ST-001</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>20</v>
+          <t>WC-ASM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Assemble Core-Coil</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>WC001</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>planned</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLAN-STARTRANS-W12</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Star Trans Week 12 Production</t>
-        </is>
+          <t>MO-ST-002</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MO-ST-002</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
+          <t>WC-WND</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pad Mount Fabrication</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>WC001</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>frozen</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -675,162 +585,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>file_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Type / Validation</t>
+          <t>project_plan (cap-svc)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PLAN_CODE</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>required; same on all rows</t>
+          <t>Schedule UI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLAN_NAME</t>
+          <t>aligned_to</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>upload-svc FILE_SCHEMAS (validator.py) as of 2026-07-18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MO_ID</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>required; must exist as erp_mo_id</t>
+          <t>Headers MUST match upload-svc (lowercase). Old 2026-07-12 templates used PRODUCT_CODE style.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OPERATION_SEQUENCE</t>
+          <t>ui</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>int; unique per MO</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OPERATION_NAME</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WORK_CENTER_CODE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>WC001|WC002|WC003…</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>START_HOUR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>number &gt;=0 hours from horizon</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DURATION_HOURS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>number &gt;0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STATUS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>planned|frozen|disrupted|ai_suggested</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NOTES</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Sample rows are illustrative. Load via SQL seed or documented importer; only project_plan uploads via UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Tenant</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>a0eebc99-9c0b-4ef8-bb6d-6bb9bd380a11</t>
+          <t>Platform → Data Upload (/platform/upload) — validate path; project plan via Planning → Schedule</t>
         </is>
       </c>
     </row>
